--- a/Result/profitability/3024.xlsx
+++ b/Result/profitability/3024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.115</v>
+        <v>0.11625</v>
       </c>
       <c r="N2" t="n">
-        <v>22.92875</v>
+        <v>23.155</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1175</v>
+        <v>0.06250000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>21.48375</v>
+        <v>22.82375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07875000000000004</v>
+        <v>0.05750000000000004</v>
       </c>
       <c r="N4" t="n">
-        <v>20.845</v>
+        <v>21.59125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03374999999999995</v>
+        <v>-0.04124999999999995</v>
       </c>
       <c r="N5" t="n">
-        <v>17.10625</v>
+        <v>18.00875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>-0.09749999999999995</v>
       </c>
       <c r="N6" t="n">
-        <v>15.01625</v>
+        <v>15.46625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="N7" t="n">
-        <v>12.83625</v>
+        <v>13.535</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1274999999999999</v>
+        <v>-0.1262499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>11.32125</v>
+        <v>11.8925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.06</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07249999999999995</v>
+        <v>-0.07249999999999997</v>
       </c>
       <c r="N13" t="n">
         <v>12.88625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>203</v>
+      </c>
+      <c r="D75" t="n">
+        <v>141</v>
+      </c>
+      <c r="E75" t="n">
+        <v>61</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.10125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.385</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1774757281553399</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.219999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3125541125541125</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
